--- a/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
+++ b/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AHIPRaceNativeHawaiianCategories</t>
+    <t>AHIPBackgroundNativeHawaiianCategories</t>
   </si>
   <si>
     <t>Title</t>
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,6 +86,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Used as the granular follow-up answer options shown when the patient selects Native Hawaiian or Other Pacific Islander on the race/ethnicity question.</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -128,12 +131,6 @@
     <t>Polynesian</t>
   </si>
   <si>
-    <t>2093-3</t>
-  </si>
-  <si>
-    <t>Kosraean</t>
-  </si>
-  <si>
     <t>2090-9</t>
   </si>
   <si>
@@ -158,12 +155,6 @@
     <t>Papua New Guinean</t>
   </si>
   <si>
-    <t>2094-1</t>
-  </si>
-  <si>
-    <t>Pohnpeian</t>
-  </si>
-  <si>
     <t>2080-0</t>
   </si>
   <si>
@@ -179,7 +170,7 @@
     <t>2098-2</t>
   </si>
   <si>
-    <t>Yapese</t>
+    <t>Yap</t>
   </si>
   <si>
     <t>System URI</t>
@@ -209,7 +200,7 @@
     <t>Please specify if not listed above</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -443,29 +434,29 @@
         <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -475,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -484,7 +475,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -492,122 +483,106 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +601,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -634,10 +609,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +625,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +647,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -680,18 +655,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -704,10 +679,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
+++ b/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -192,12 +192,6 @@
   </si>
   <si>
     <t>I choose not to respond at this time</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
@@ -638,7 +632,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -663,26 +657,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
+++ b/docs/ValueSet-ahip-background-native-hawaiian-category.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -95,7 +95,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>Most of the information on the CDC and ATSDR websites is not subject to copyright, is in the public domain, and may be freely used or reproduced without obtaining copyright permission. For information and exceptions regarding use of CDC material please see https://www.cdc.gov/other/agencymaterials.html.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -131,6 +133,12 @@
     <t>Polynesian</t>
   </si>
   <si>
+    <t>2093-3</t>
+  </si>
+  <si>
+    <t>Kosraean</t>
+  </si>
+  <si>
     <t>2090-9</t>
   </si>
   <si>
@@ -155,6 +163,12 @@
     <t>Papua New Guinean</t>
   </si>
   <si>
+    <t>2094-1</t>
+  </si>
+  <si>
+    <t>Pohnpeian</t>
+  </si>
+  <si>
     <t>2080-0</t>
   </si>
   <si>
@@ -170,7 +184,7 @@
     <t>2098-2</t>
   </si>
   <si>
-    <t>Yap</t>
+    <t>Yapese</t>
   </si>
   <si>
     <t>System URI</t>
@@ -194,7 +208,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -460,7 +474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -565,18 +579,34 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -603,10 +633,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -619,10 +649,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -649,10 +679,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
@@ -665,10 +695,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
